--- a/config.xlsx
+++ b/config.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="Ra51c46e656c74017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopWinners" sheetId="2" r:id="R35c1992a6e3a4a22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DoDont" sheetId="3" r:id="R76bff1fde7024906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="4" r:id="Rd564122812d44844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TeamMembers" sheetId="5" r:id="R8609f31e1f7b4de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboards" sheetId="6" r:id="Rc22756e3621a49dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WinnersArchive" sheetId="7" r:id="R3ce9e812e5e242c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HomeRounds" sheetId="8" r:id="Ra9e30d8723804fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormQuestions" sheetId="9" r:id="Rbe4347ed9c554bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="10" r:id="R8fe588eafd344b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="R2c3689c7cfd54039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopWinners" sheetId="2" r:id="R19f3958755f9496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DoDont" sheetId="3" r:id="Rcec35cb3a9ff45fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ" sheetId="4" r:id="Rdbf4537c6a214117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TeamMembers" sheetId="5" r:id="R1273c0398fe649b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboards" sheetId="6" r:id="R6ef6a19eb5804319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WinnersArchive" sheetId="7" r:id="R8a4fb6e9f3fd43ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HomeRounds" sheetId="8" r:id="Rdaba6f61ec4a4b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormQuestions" sheetId="9" r:id="Rc4dd6852821c4e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="10" r:id="R29d2a02e7a224cf9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -386,7 +386,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="84">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -650,6 +650,13 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -712,8 +719,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="NzReadMe" displayName="NzReadMe" ref="A1:B14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:B14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="NzReadMe" displayName="NzReadMe" ref="A1:B19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:B19"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Instructions"/>
@@ -1097,8 +1104,8 @@
         <x:v>announcement_en</x:v>
       </x:c>
       <x:c r="B15" s="33" t="str">
-        <x:f>"Four weekly rounds each month. Earn "&amp;'Settings'!$B$39&amp;" participation points plus "&amp;'Settings'!$B$40&amp;" points for a correct answer per round, up to "&amp;(4*('Settings'!$B$39+'Settings'!$B$40))&amp;" points per month. Recognition is through published names and points, with no programme cash prizes or vouchers."</x:f>
-        <x:v>Four weekly rounds each month. Earn 5 participation points plus 5 points for a correct answer per round, up to 40 points per month. Recognition is through published names and points, with no programme cash prizes or vouchers.</x:v>
+        <x:f>"Nazaha Minute offers four weekly rounds, up to "&amp;(4*('Settings'!$B$39+'Settings'!$B$40))&amp;" points per month. Other verified activities also count. Annual recognition consideration starts at "&amp;'Settings'!$B$45&amp;" points. Recognition is through names and points, with no programme cash prizes, gifts or vouchers."</x:f>
+        <x:v>Nazaha Minute offers four weekly rounds, up to 40 points per month. Other verified activities also count. Annual recognition consideration starts at 400 points. Recognition is through names and points, with no programme cash prizes, gifts or vouchers.</x:v>
       </x:c>
       <x:c r="C15" s="33" t="str">
         <x:v>New monthly programme. The displayed score values follow the Settings inputs.</x:v>
@@ -1396,14 +1403,146 @@
         <x:v>config_version</x:v>
       </x:c>
       <x:c r="B43" s="31" t="str">
-        <x:v>2.0</x:v>
+        <x:v>3.0</x:v>
       </x:c>
       <x:c r="C43" s="31" t="str">
-        <x:v>Four weekly rounds per month, points recognition and English content. Main version 2 reads the new HomeRounds sheet.</x:v>
+        <x:v>Points page version 3 adds activity categories and calendar-year eligibility. Existing page, media and team links are retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="60" customHeight="1">
+      <x:c r="A44" s="33" t="str">
+        <x:v>points_rules_version</x:v>
+      </x:c>
+      <x:c r="B44" s="83" t="str">
+        <x:v>3.0</x:v>
+      </x:c>
+      <x:c r="C44" s="33" t="str">
+        <x:v>Points page schema. Nazaha Minute and the five activity categories contribute to annual recognition.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="60" customHeight="1">
+      <x:c r="A45" s="33" t="str">
+        <x:v>points_annual_eligibility</x:v>
+      </x:c>
+      <x:c r="B45" s="58" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="C45" s="33" t="str">
+        <x:v>Minimum verified calendar-year total for annual consideration. Eligibility does not guarantee selection. Must be greater than 300.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="60" customHeight="1">
+      <x:c r="A46" s="33" t="str">
+        <x:v>points_knowledge</x:v>
+      </x:c>
+      <x:c r="B46" s="58" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C46" s="33" t="str">
+        <x:v>Points for an approved quarterly ethics quiz or training, separate from Nazaha Minute.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="60" customHeight="1">
+      <x:c r="A47" s="33" t="str">
+        <x:v>points_initiative</x:v>
+      </x:c>
+      <x:c r="B47" s="58" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C47" s="33" t="str">
+        <x:v>Points for an eligible improvement or issue submission confirmed by the authorised team. No confidential case details in this workbook.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="60" customHeight="1">
+      <x:c r="A48" s="33" t="str">
+        <x:v>points_engagement</x:v>
+      </x:c>
+      <x:c r="B48" s="58" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C48" s="33" t="str">
+        <x:v>Points per verified ethics workshop or awareness session.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="60" customHeight="1">
+      <x:c r="A49" s="33" t="str">
+        <x:v>points_recognition</x:v>
+      </x:c>
+      <x:c r="B49" s="58" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C49" s="33" t="str">
+        <x:v>Points for an approved line-manager recognition with justification and evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="60" customHeight="1">
+      <x:c r="A50" s="33" t="str">
+        <x:v>points_peer_nomination</x:v>
+      </x:c>
+      <x:c r="B50" s="58" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C50" s="33" t="str">
+        <x:v>Points to the nominator for an approved ethical-role-model nomination with a justification of up to 50 words. No automatic points to the nominee.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="60" customHeight="1">
+      <x:c r="A51" s="33" t="str">
+        <x:v>points_knowledge_per_quarter</x:v>
+      </x:c>
+      <x:c r="B51" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C51" s="33" t="str">
+        <x:v>Maximum credited knowledge activities per employee per calendar quarter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="60" customHeight="1">
+      <x:c r="A52" s="33" t="str">
+        <x:v>points_initiative_per_quarter</x:v>
+      </x:c>
+      <x:c r="B52" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C52" s="33" t="str">
+        <x:v>Maximum credited distinct initiatives per employee per calendar quarter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="60" customHeight="1">
+      <x:c r="A53" s="33" t="str">
+        <x:v>points_engagement_per_quarter</x:v>
+      </x:c>
+      <x:c r="B53" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C53" s="33" t="str">
+        <x:v>Maximum credited distinct sessions per employee per calendar quarter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="60" customHeight="1">
+      <x:c r="A54" s="33" t="str">
+        <x:v>points_recognition_per_year</x:v>
+      </x:c>
+      <x:c r="B54" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C54" s="33" t="str">
+        <x:v>Maximum approved manager recognitions per employee per calendar year.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="60" customHeight="1">
+      <x:c r="A55" s="33" t="str">
+        <x:v>points_peer_nomination_per_month</x:v>
+      </x:c>
+      <x:c r="B55" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C55" s="33" t="str">
+        <x:v>Maximum approved peer nominations credited to a nominator per calendar month.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="13">
     <x:dataValidation type="whole" operator="between" sqref="B39">
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
@@ -1412,15 +1551,59 @@
       <x:formula1>0</x:formula1>
       <x:formula2>100</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B45">
+      <x:formula1>301</x:formula1>
+      <x:formula2>10000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B46">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B47">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B48">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B49">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B50">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B51">
+      <x:formula1>1</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B52">
+      <x:formula1>1</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B53">
+      <x:formula1>1</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B54">
+      <x:formula1>1</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B55">
+      <x:formula1>1</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="R98f77d2394274c7b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="R44f8a6eaa3774ca3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="Rf0fbaad0bb084d8f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="R7418ced4eaa341d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="Redb6667ff3a94669"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R9f2a4d86c4df45ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="Re91f482c4cb14471"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="R544d646f824e4f10"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="Re78c7cdf6753424b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="Rf14d100704944f40"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="Rc3120437a8b74e7e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R003bfe16126740c7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R0dd25a567b714477"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="R04dbb10a4ee34378"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1501,12 +1684,12 @@
         <x:v>Use a unique record key based on the verified account, campaign period and round. Treat workflow retries as the same response. Count only the first eligible response per round. Derive totals from the eligible records instead of repeatedly adding points on retries. Agree and publish a rule for equal totals before generating ranked results.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="57" customHeight="1">
+    <x:row r="9" ht="70" customHeight="1">
       <x:c r="A9" s="31" t="str">
         <x:v>Point inputs</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>The participation and accuracy inputs are in Settings. Related FAQ answers and the announcement calculate from those cells. The current rule is one scored question per round. If point inputs change, update and check the scoring workflow before opening the affected campaign. Do not recalculate historical campaigns using a new rule.</x:v>
+        <x:v>Settings holds Nazaha Minute rates and the version 3 activity rates, frequency limits and annual eligibility threshold. Related FAQ text and the announcement link to these inputs. Update the protected scoring workflow to match before launch. Preserve the rule version attached to historical activities; do not recalculate old records at new rates.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
@@ -1549,10 +1732,50 @@
         <x:v>For a new cycle, update round descriptions and FormQuestions, create the new forms and replace the schedule and URLs. Update FAQ or DoDont when the source guidance changes. Keep actual presenter details accurate and preserve the existing media image paths and dimensions.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="33" t="str">
+        <x:v>Activity verification</x:v>
+      </x:c>
+      <x:c r="B15" s="33" t="str">
+        <x:v>Minute uses the first eligible account response in the published window. Other categories require authorised verification and a distinct activity identifier. Knowledge and engagement must be separate activities from Minute. Reuse of one contribution under another category earns no additional points.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="33" t="str">
+        <x:v>Category limits</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="str">
+        <x:v>Settings defines limits of 1 knowledge, 2 initiative and 2 engagement activities per calendar quarter, 2 manager recognitions per calendar year and 1 approved peer nomination per calendar month. These defaults can be revised in Settings and the scoring workflow together. The nomination points belong to the nominator.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="33" t="str">
+        <x:v>Annual eligibility</x:v>
+      </x:c>
+      <x:c r="B17" s="33" t="str">
+        <x:v>The default annual threshold is 400 verified points, greater than 300. The recognition year is 1 January to 31 December in Oman time. Attribute activity credit to the eligible activity date, not delayed approval time. The threshold is an eligibility floor, not a promised award or a monthly/quarterly listing requirement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="33" t="str">
+        <x:v>Confidential initiative credit</x:v>
+      </x:c>
+      <x:c r="B18" s="33" t="str">
+        <x:v>Keep Speaking Up content and case identities outside this public workbook and published score records. Only the authorised team may confirm any eligible initiative credit privately. Do not make reporting access or confidentiality depend on programme points.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="33" t="str">
+        <x:v>Page and workflow versions</x:v>
+      </x:c>
+      <x:c r="B19" s="33" t="str">
+        <x:v>Use Points &amp; Recognition page version 3 with these settings. The calculator only illustrates annual totals and does not submit, save or award points. Forms links and dates remain blank. Existing automatic-scoring connections have not been created or activated by this update.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2b6b4144524983"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bbf9048864e439d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2272,16 +2495,16 @@
         <x:v>Nazaha participation model</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="57" customHeight="1">
+    <x:row r="4" ht="92" customHeight="1">
       <x:c r="A4" s="33" t="str">
         <x:v>Participation</x:v>
       </x:c>
       <x:c r="B4" s="33" t="str">
-        <x:v>Are the monthly challenges mandatory?</x:v>
+        <x:v>Is participation in Nazaha Minute mandatory?</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str"/>
       <x:c r="D4" s="33" t="str">
-        <x:v>The monthly challenges are voluntary learning activities. They do not replace your obligations to follow the Code of Conduct, complete the annual declaration and complete mandatory training.</x:v>
+        <x:v>Nazaha Minute and the points programme are voluntary. They do not replace the duty to follow the Code of Conduct, complete the annual declaration or complete mandatory training.</x:v>
       </x:c>
       <x:c r="E4" s="33" t="str"/>
       <x:c r="F4" s="53" t="b">
@@ -2291,20 +2514,20 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="57" t="str">
-        <x:v>Nazaha participation model; Code of Conduct, Section 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="90" customHeight="1">
+        <x:v>Nazaha programme; Code of Conduct, Section 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="92" customHeight="1">
       <x:c r="A5" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
       <x:c r="B5" s="33" t="str">
-        <x:v>How do I earn points in a round?</x:v>
+        <x:v>How do I earn points in a Nazaha Minute round?</x:v>
       </x:c>
       <x:c r="C5" s="33" t="str"/>
       <x:c r="D5" s="33" t="str">
-        <x:f>"Earn "&amp;'Settings'!$B$39&amp;" points for one eligible response, plus "&amp;'Settings'!$B$40&amp;" additional points for the correct answer. The maximum is "&amp;('Settings'!$B$39+'Settings'!$B$40)&amp;" points per round. Use your work account and submit within the published round window."</x:f>
-        <x:v>Earn 5 points for one eligible response, plus 5 additional points for the correct answer. The maximum is 10 points per round. Use your work account and submit within the published round window.</x:v>
+        <x:f>"Earn "&amp;'Settings'!$B$39&amp;" points for one eligible first response, plus "&amp;'Settings'!$B$40&amp;" additional points for a correct first answer. The maximum is "&amp;('Settings'!$B$39+'Settings'!$B$40)&amp;" points per round. Use your work account and submit within the published round window."</x:f>
+        <x:v>Earn 5 points for one eligible first response, plus 5 additional points for a correct first answer. The maximum is 10 points per round. Use your work account and submit within the published round window.</x:v>
       </x:c>
       <x:c r="E5" s="33" t="str"/>
       <x:c r="F5" s="53" t="b">
@@ -2314,20 +2537,20 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="57" t="str">
-        <x:v>Settings.home_participation_points; Settings.home_accuracy_points</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="90" customHeight="1">
+        <x:v>Nazaha programme point rules</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="92" customHeight="1">
       <x:c r="A6" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
       <x:c r="B6" s="33" t="str">
-        <x:v>What is the maximum monthly score?</x:v>
+        <x:v>What is the maximum monthly score for Nazaha Minute?</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str"/>
       <x:c r="D6" s="33" t="str">
-        <x:f>"There are four rounds per month. With the current rules, each round offers up to "&amp;('Settings'!$B$39+'Settings'!$B$40)&amp;" points, giving a maximum of "&amp;(4*('Settings'!$B$39+'Settings'!$B$40))&amp;" points per month."</x:f>
-        <x:v>There are four rounds per month. With the current rules, each round offers up to 10 points, giving a maximum of 40 points per month.</x:v>
+        <x:f>"Four rounds offer up to "&amp;('Settings'!$B$39+'Settings'!$B$40)&amp;" points each, giving a maximum of "&amp;(4*('Settings'!$B$39+'Settings'!$B$40))&amp;" Nazaha Minute points per month. This limit applies only to Nazaha Minute. Other eligible activity categories add to the programme total."</x:f>
+        <x:v>Four rounds offer up to 10 points each, giving a maximum of 40 Nazaha Minute points per month. This limit applies only to Nazaha Minute. Other eligible activity categories add to the programme total.</x:v>
       </x:c>
       <x:c r="E6" s="33" t="str"/>
       <x:c r="F6" s="53" t="b">
@@ -2337,7 +2560,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H6" s="57" t="str">
-        <x:v>Four rounds; Settings point inputs</x:v>
+        <x:v>Nazaha programme point rules</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="90" customHeight="1">
@@ -2363,7 +2586,7 @@
         <x:v>Settings.home_participation_points; Settings.home_accuracy_points</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="57" customHeight="1">
+    <x:row r="8" ht="92" customHeight="1">
       <x:c r="A8" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
@@ -2372,7 +2595,7 @@
       </x:c>
       <x:c r="C8" s="33" t="str"/>
       <x:c r="D8" s="33" t="str">
-        <x:v>Points appear after the response has been validated and the results have been published. A form submission confirmation does not mean the leaderboard has already refreshed. Check the published reporting period.</x:v>
+        <x:v>Points appear after responses or other eligible activities have been verified and the results published. A submission confirmation does not mean points are awarded or the leaderboard has refreshed. Check the published reporting period.</x:v>
       </x:c>
       <x:c r="E8" s="33" t="str"/>
       <x:c r="F8" s="53" t="b">
@@ -2382,7 +2605,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H8" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
+        <x:v>Nazaha programme point rules</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="57" customHeight="1">
@@ -2495,7 +2718,7 @@
         <x:v>Nazaha participation model</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="57" customHeight="1">
+    <x:row r="14" ht="92" customHeight="1">
       <x:c r="A14" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
@@ -2504,7 +2727,7 @@
       </x:c>
       <x:c r="C14" s="33" t="str"/>
       <x:c r="D14" s="33" t="str">
-        <x:v>Points in this programme come from eligible challenge responses. Browsing the portal, watching media, opening the Code of Conduct and using the Integrity Guide do not award challenge points.</x:v>
+        <x:v>Page visits, downloads, media views and practice activities do not award points. Eligible Nazaha Minute responses, approved knowledge activities, initiatives, verified sessions, manager recognition and approved peer nominations can count under their published limits.</x:v>
       </x:c>
       <x:c r="E14" s="33" t="str"/>
       <x:c r="F14" s="53" t="b">
@@ -2514,7 +2737,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H14" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
+        <x:v>Nazaha programme point rules</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
@@ -2539,16 +2762,16 @@
         <x:v>Code of Conduct, Sections 12 and 13; Nazaha participation model</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="57" customHeight="1">
+    <x:row r="16" ht="92" customHeight="1">
       <x:c r="A16" s="33" t="str">
         <x:v>Recognition</x:v>
       </x:c>
       <x:c r="B16" s="33" t="str">
-        <x:v>Are there cash prizes, vouchers or gifts for challenge points?</x:v>
+        <x:v>Are there cash prizes, vouchers or gifts for programme points?</x:v>
       </x:c>
       <x:c r="C16" s="33" t="str"/>
       <x:c r="D16" s="33" t="str">
-        <x:v>The monthly learning programme offers recognition through points and published names. It does not offer cash prizes, vouchers or gifts.</x:v>
+        <x:v>Programme recognition is through points and published names. The points programme does not offer cash prizes, vouchers or gifts.</x:v>
       </x:c>
       <x:c r="E16" s="33" t="str"/>
       <x:c r="F16" s="53" t="b">
@@ -2558,7 +2781,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H16" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
+        <x:v>Nazaha programme point rules</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="57" customHeight="1">
@@ -2583,7 +2806,7 @@
         <x:v>Nazaha portal publication model</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="72" customHeight="1">
+    <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="33" t="str">
         <x:v>Recognition</x:v>
       </x:c>
@@ -2592,7 +2815,7 @@
       </x:c>
       <x:c r="C18" s="33" t="str"/>
       <x:c r="D18" s="33" t="str">
-        <x:v>Quarterly totals add the eligible points earned during the three calendar months in that quarter. Monthly scores are included once. A new quarter starts a new total, while previously published results remain in the archive.</x:v>
+        <x:v>Quarterly totals include eligible, verified points from all programme categories in the three calendar months of that quarter. Count each activity once. Use the eligible activity date in Oman time and enforce category limits within their relevant month, quarter or year.</x:v>
       </x:c>
       <x:c r="E18" s="33" t="str"/>
       <x:c r="F18" s="53" t="b">
@@ -2602,10 +2825,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H18" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="57" customHeight="1">
+        <x:v>Nazaha programme point rules</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="92" customHeight="1">
       <x:c r="A19" s="33" t="str">
         <x:v>Recognition</x:v>
       </x:c>
@@ -2614,7 +2837,7 @@
       </x:c>
       <x:c r="C19" s="33" t="str"/>
       <x:c r="D19" s="33" t="str">
-        <x:v>Results are checked against the official response records before publication. Duplicate or ineligible submissions do not count. If a score is corrected, the affected totals and standings must be updated together.</x:v>
+        <x:v>Results are checked against official response and approved activity records. Duplicate or ineligible claims do not count. The same contribution cannot be credited twice under different categories. Corrections must update all affected period totals and standings together.</x:v>
       </x:c>
       <x:c r="E19" s="33" t="str"/>
       <x:c r="F19" s="53" t="b">
@@ -2624,10 +2847,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H19" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="57" customHeight="1">
+        <x:v>Nazaha programme point rules</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="92" customHeight="1">
       <x:c r="A20" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
@@ -2636,7 +2859,7 @@
       </x:c>
       <x:c r="C20" s="33" t="str"/>
       <x:c r="D20" s="33" t="str">
-        <x:v>Each month has its own score. Previous monthly scores remain part of the relevant quarterly total and published history. They are not added again as new points in the next month.</x:v>
+        <x:v>Each month has its own total. Eligible activities also contribute once to their calendar-quarter and calendar-year totals. Do not add overlapping monthly, quarterly and annual totals together. Annual eligibility starts afresh on 1 January; historical results remain in their original year.</x:v>
       </x:c>
       <x:c r="E20" s="33" t="str"/>
       <x:c r="F20" s="53" t="b">
@@ -2646,19 +2869,20 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H20" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="72" customHeight="1">
+        <x:v>Nazaha programme point rules</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="135" customHeight="1">
       <x:c r="A21" s="33" t="str">
         <x:v>Points</x:v>
       </x:c>
       <x:c r="B21" s="33" t="str">
-        <x:v>Do the old activity categories and annual points threshold still apply?</x:v>
+        <x:v>Which activities count towards annual recognition?</x:v>
       </x:c>
       <x:c r="C21" s="33" t="str"/>
       <x:c r="D21" s="33" t="str">
-        <x:v>The new programme uses four monthly rounds and the published response scoring rules. Previous activity categories and the annual recognition threshold are not used to score these rounds. Any genuine historical results should remain in their original reporting period.</x:v>
+        <x:f>"Nazaha Minute replaces the former Monthly Challenge. Knowledge earns "&amp;'Settings'!$B$46&amp;" points, initiative "&amp;'Settings'!$B$47&amp;", engagement "&amp;'Settings'!$B$48&amp;", approved manager recognition "&amp;'Settings'!$B$49&amp;" and approved peer nomination "&amp;'Settings'!$B$50&amp;" to the nominator. Published category limits apply. At least "&amp;'Settings'!$B$45&amp;" verified calendar-year points are required for annual consideration. Eligibility does not guarantee selection. This threshold does not restrict monthly or quarterly listings."</x:f>
+        <x:v>Nazaha Minute replaces the former Monthly Challenge. Knowledge earns 20 points, initiative 30, engagement 15, approved manager recognition 40 and approved peer nomination 10 to the nominator. Published category limits apply. At least 400 verified calendar-year points are required for annual consideration. Eligibility does not guarantee selection. This threshold does not restrict monthly or quarterly listings.</x:v>
       </x:c>
       <x:c r="E21" s="33" t="str"/>
       <x:c r="F21" s="53" t="b">
@@ -2668,7 +2892,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H21" s="57" t="str">
-        <x:v>Nazaha participation model</x:v>
+        <x:v>Nazaha programme point rules</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="57" customHeight="1">
@@ -3333,10 +3557,10 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="Rbf808fc1ffc14134"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="R0bb41f5da4c04214"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="R34d2fefc72ef4cea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="Rf275e5d180954b99"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="Rfa0291b2f1ee4406"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="R54cf08ca02784971"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="R9dc40dc697da4b88"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="Rc8898280f6a3443c"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3892,7 +4116,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66e38181bfbe4453"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R874717e24dfa4b94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4047,7 +4271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5918685e7ef04e05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13aef44127e74040"/>
   </x:tableParts>
 </x:worksheet>
 </file>